--- a/main/ValueSet-MatchCreationTypeVS.xlsx
+++ b/main/ValueSet-MatchCreationTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:07:42+00:00</t>
+    <t>2026-09-17T12:28:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ValueSet-MatchCreationTypeVS.xlsx
+++ b/main/ValueSet-MatchCreationTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:28:54+00:00</t>
+    <t>2026-09-17T14:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ValueSet-MatchCreationTypeVS.xlsx
+++ b/main/ValueSet-MatchCreationTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:43:24+00:00</t>
+    <t>2026-09-22T12:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ValueSet-MatchCreationTypeVS.xlsx
+++ b/main/ValueSet-MatchCreationTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:29:02+00:00</t>
+    <t>2026-10-01T16:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
